--- a/rental_application_form_templates/047_rental_reference_request--rental_application_form_templates.xlsx
+++ b/rental_application_form_templates/047_rental_reference_request--rental_application_form_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -919,8 +919,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -948,12 +948,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'parent',_'value':_'parent'}</t>
+          <t>parent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Parent', 'value': 'Parent'}</t>
+          <t>Parent</t>
         </is>
       </c>
     </row>
@@ -965,12 +965,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'spouse',_'value':_'spouse'}</t>
+          <t>spouse</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Spouse', 'value': 'Spouse'}</t>
+          <t>Spouse</t>
         </is>
       </c>
     </row>
@@ -982,12 +982,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'friend',_'value':_'friend'}</t>
+          <t>friend</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Friend', 'value': 'Friend'}</t>
+          <t>Friend</t>
         </is>
       </c>
     </row>
@@ -999,12 +999,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'family_member',_'value':_'family_member'}</t>
+          <t>family_member</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Family Member', 'value': 'Family Member'}</t>
+          <t>Family Member</t>
         </is>
       </c>
     </row>
@@ -1016,12 +1016,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1033,12 +1033,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'signature_provided',_'value':_'signature_provided'}</t>
+          <t>signature_provided</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Signature Provided', 'value': 'Signature Provided'}</t>
+          <t>Signature Provided</t>
         </is>
       </c>
     </row>
@@ -1050,12 +1050,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_none,_'value':_none}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': None, 'value': None}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_none,_'value':_none}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': None, 'value': None}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
